--- a/data/trans_camb/IP11A_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP11A_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -629,22 +629,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>19,14</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 52,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,37</t>
+          <t>0,0; 25,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,22 +735,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,81</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,31</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7,15</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>29,65</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,84</t>
+          <t>27,76</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>19,58</t>
+          <t>17,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,24</t>
+          <t>0,0; 39,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 17,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,0</t>
+          <t>0,0; 63,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 9,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,87</t>
+          <t>0,0; 20,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 52,86</t>
+          <t>4,98; 42,91</t>
         </is>
       </c>
     </row>
@@ -946,27 +946,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1056,34 +1056,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,01</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,97</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,71</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,01</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,97</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,73</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>-0,84</t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>3,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-19,32; 6,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,51; 24,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,63; 49,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 7,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 23,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 45,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 4,83</t>
+          <t>-9,98; 4,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 19,23</t>
+          <t>-6,42; 17,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 29,3</t>
+          <t>-6,44; 29,42</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-36,78%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35,99%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>140,67%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-36,78%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>122,93%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-26,3%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>113,25%</t>
+          <t>123,04%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,76</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-6,47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-12,53</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>26,13</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,76</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-6,47</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-12,53</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-24,87; 16,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,3</t>
+          <t>-31,03; 12,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-37,38; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 18,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,65; 11,94</t>
+          <t>0,0; 76,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-37,5; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 11,14</t>
+          <t>-13,49; 11,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 22,49</t>
+          <t>-10,28; 21,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 0,0</t>
+          <t>-20,91; 0,0</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-22,01%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-51,63%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-22,01%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-51,63%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,49</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,07</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,37</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>11,77</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>7,83</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>7,45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>4,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>-6,08; 5,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,27; 26,87</t>
+          <t>-6,41; 6,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,91</t>
+          <t>-4,26; 21,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 5,32</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 6,6</t>
+          <t>3,33; 26,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 20,77</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 4,02</t>
+          <t>-3,19; 4,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 10,27</t>
+          <t>-0,57; 10,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 15,73</t>
+          <t>-0,78; 14,75</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1594,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-12,46%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-18,59%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>78,3%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-12,46%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-18,59%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>81,35%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>15,74%</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>232,36%</t>
+          <t>222,53%</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,16; —</t>
+          <t>-51,15; 2258,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
